--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2074,6 +2074,1061 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128802152</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91010</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>557969</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6944681</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ungt exemplar, därför osäker artbestämning.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128802084</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>558061</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6944713</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>På liggande död sälg.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea # På liggande död sälg.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128802087</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>558071</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6944707</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128802083</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>557957</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6944719</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128802082</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>557934</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6944733</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128802085</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>558062</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6944711</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128802081</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>557928</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6944723</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128802089</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>558071</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6944723</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128802088</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>558072</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6944719</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>På stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea # På stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128802086</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80194</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Marktjärn, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>558041</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6944734</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2079,7 +2079,7 @@
         <v>128802152</v>
       </c>
       <c r="B14" t="n">
-        <v>91010</v>
+        <v>91037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>128802084</v>
       </c>
       <c r="B15" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128802087</v>
       </c>
       <c r="B16" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>128802083</v>
       </c>
       <c r="B17" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128802082</v>
       </c>
       <c r="B18" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128802085</v>
       </c>
       <c r="B19" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>128802081</v>
       </c>
       <c r="B20" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128802089</v>
       </c>
       <c r="B21" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128802088</v>
+        <v>128802086</v>
       </c>
       <c r="B22" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558072</v>
+        <v>558041</v>
       </c>
       <c r="R22" t="n">
-        <v>6944719</v>
+        <v>6944734</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,26 +2990,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>På stående död sälg.</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea # På stående död sälg.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3030,10 +3010,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128802086</v>
+        <v>128802088</v>
       </c>
       <c r="B23" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,10 +3045,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558041</v>
+        <v>558072</v>
       </c>
       <c r="R23" t="n">
-        <v>6944734</v>
+        <v>6944719</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,6 +3091,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>På stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea # På stående död sälg.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2909,7 +2909,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128802086</v>
+        <v>128802088</v>
       </c>
       <c r="B22" t="n">
         <v>80221</v>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558041</v>
+        <v>558072</v>
       </c>
       <c r="R22" t="n">
-        <v>6944734</v>
+        <v>6944719</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,6 +2990,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>På stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea # På stående död sälg.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3010,7 +3030,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128802088</v>
+        <v>128802086</v>
       </c>
       <c r="B23" t="n">
         <v>80221</v>
@@ -3045,10 +3065,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558072</v>
+        <v>558041</v>
       </c>
       <c r="R23" t="n">
-        <v>6944719</v>
+        <v>6944734</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3091,26 +3111,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>På stående död sälg.</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Salix caprea # På stående död sälg.</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2079,7 +2079,7 @@
         <v>128802152</v>
       </c>
       <c r="B14" t="n">
-        <v>91037</v>
+        <v>91042</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>128802084</v>
       </c>
       <c r="B15" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128802087</v>
       </c>
       <c r="B16" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>128802083</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128802082</v>
       </c>
       <c r="B18" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128802085</v>
       </c>
       <c r="B19" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>128802081</v>
       </c>
       <c r="B20" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128802089</v>
       </c>
       <c r="B21" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>128802088</v>
       </c>
       <c r="B22" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>128802086</v>
       </c>
       <c r="B23" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2079,7 +2079,7 @@
         <v>128802152</v>
       </c>
       <c r="B14" t="n">
-        <v>91042</v>
+        <v>91047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2079,7 +2079,7 @@
         <v>128802152</v>
       </c>
       <c r="B14" t="n">
-        <v>91047</v>
+        <v>91051</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>128802084</v>
       </c>
       <c r="B15" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128802087</v>
       </c>
       <c r="B16" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>128802083</v>
       </c>
       <c r="B17" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128802082</v>
       </c>
       <c r="B18" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128802085</v>
       </c>
       <c r="B19" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>128802081</v>
       </c>
       <c r="B20" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128802089</v>
       </c>
       <c r="B21" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>128802088</v>
       </c>
       <c r="B22" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>128802086</v>
       </c>
       <c r="B23" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2909,7 +2909,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128802088</v>
+        <v>128802086</v>
       </c>
       <c r="B22" t="n">
         <v>80229</v>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558072</v>
+        <v>558041</v>
       </c>
       <c r="R22" t="n">
-        <v>6944719</v>
+        <v>6944734</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,26 +2990,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>På stående död sälg.</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea # På stående död sälg.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3030,7 +3010,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128802086</v>
+        <v>128802088</v>
       </c>
       <c r="B23" t="n">
         <v>80229</v>
@@ -3065,10 +3045,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558041</v>
+        <v>558072</v>
       </c>
       <c r="R23" t="n">
-        <v>6944734</v>
+        <v>6944719</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,6 +3091,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>På stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea # På stående död sälg.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2909,7 +2909,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128802086</v>
+        <v>128802088</v>
       </c>
       <c r="B22" t="n">
         <v>80229</v>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558041</v>
+        <v>558072</v>
       </c>
       <c r="R22" t="n">
-        <v>6944734</v>
+        <v>6944719</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,6 +2990,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>På stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea # På stående död sälg.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3010,7 +3030,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128802088</v>
+        <v>128802086</v>
       </c>
       <c r="B23" t="n">
         <v>80229</v>
@@ -3045,10 +3065,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558072</v>
+        <v>558041</v>
       </c>
       <c r="R23" t="n">
-        <v>6944719</v>
+        <v>6944734</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3091,26 +3111,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>På stående död sälg.</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Salix caprea # På stående död sälg.</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2079,7 +2079,7 @@
         <v>128802152</v>
       </c>
       <c r="B14" t="n">
-        <v>91051</v>
+        <v>91056</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>128802084</v>
       </c>
       <c r="B15" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128802087</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>128802083</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128802082</v>
       </c>
       <c r="B18" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128802085</v>
       </c>
       <c r="B19" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>128802081</v>
       </c>
       <c r="B20" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128802089</v>
       </c>
       <c r="B21" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>128802088</v>
       </c>
       <c r="B22" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>128802086</v>
       </c>
       <c r="B23" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2079,7 +2079,7 @@
         <v>128802152</v>
       </c>
       <c r="B14" t="n">
-        <v>91063</v>
+        <v>91066</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2079,7 +2079,7 @@
         <v>128802152</v>
       </c>
       <c r="B14" t="n">
-        <v>91066</v>
+        <v>91069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>128802084</v>
       </c>
       <c r="B15" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128802087</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>128802083</v>
       </c>
       <c r="B17" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128802082</v>
       </c>
       <c r="B18" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128802085</v>
       </c>
       <c r="B19" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>128802081</v>
       </c>
       <c r="B20" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128802089</v>
       </c>
       <c r="B21" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>128802088</v>
       </c>
       <c r="B22" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>128802086</v>
       </c>
       <c r="B23" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>129092677</v>
       </c>
       <c r="B24" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>129092675</v>
       </c>
       <c r="B25" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -3232,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129092675</v>
+        <v>129092674</v>
       </c>
       <c r="B25" t="n">
-        <v>80140</v>
+        <v>57673</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,21 +3243,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>102110</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3267,13 +3267,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558199</v>
+        <v>558159</v>
       </c>
       <c r="R25" t="n">
-        <v>6944768</v>
+        <v>6944689</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129092674</v>
+        <v>129092675</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102110</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558159</v>
+        <v>558199</v>
       </c>
       <c r="R26" t="n">
-        <v>6944689</v>
+        <v>6944768</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2079,7 +2079,7 @@
         <v>128802152</v>
       </c>
       <c r="B14" t="n">
-        <v>91069</v>
+        <v>91073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>128802084</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128802087</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>128802083</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128802082</v>
       </c>
       <c r="B18" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128802085</v>
       </c>
       <c r="B19" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>128802081</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128802089</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128802088</v>
+        <v>128802086</v>
       </c>
       <c r="B22" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558072</v>
+        <v>558041</v>
       </c>
       <c r="R22" t="n">
-        <v>6944719</v>
+        <v>6944734</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,26 +2990,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>På stående död sälg.</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea # På stående död sälg.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3030,10 +3010,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128802086</v>
+        <v>128802088</v>
       </c>
       <c r="B23" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,10 +3045,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558041</v>
+        <v>558072</v>
       </c>
       <c r="R23" t="n">
-        <v>6944734</v>
+        <v>6944719</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,6 +3091,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>På stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea # På stående död sälg.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3134,7 +3134,7 @@
         <v>129092677</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129092674</v>
+        <v>129092675</v>
       </c>
       <c r="B25" t="n">
-        <v>57673</v>
+        <v>80144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,21 +3243,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102110</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3267,13 +3267,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558159</v>
+        <v>558199</v>
       </c>
       <c r="R25" t="n">
-        <v>6944689</v>
+        <v>6944768</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129092675</v>
+        <v>129092674</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>57675</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>102110</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558199</v>
+        <v>558159</v>
       </c>
       <c r="R26" t="n">
-        <v>6944768</v>
+        <v>6944689</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -3232,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129092675</v>
+        <v>129092674</v>
       </c>
       <c r="B25" t="n">
-        <v>80144</v>
+        <v>57675</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,21 +3243,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>102110</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3267,13 +3267,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558199</v>
+        <v>558159</v>
       </c>
       <c r="R25" t="n">
-        <v>6944768</v>
+        <v>6944689</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129092674</v>
+        <v>129092675</v>
       </c>
       <c r="B26" t="n">
-        <v>57675</v>
+        <v>80144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102110</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558159</v>
+        <v>558199</v>
       </c>
       <c r="R26" t="n">
-        <v>6944689</v>
+        <v>6944768</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2079,7 +2079,7 @@
         <v>128802152</v>
       </c>
       <c r="B14" t="n">
-        <v>91073</v>
+        <v>91080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128802086</v>
+        <v>128802088</v>
       </c>
       <c r="B22" t="n">
         <v>80144</v>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558041</v>
+        <v>558072</v>
       </c>
       <c r="R22" t="n">
-        <v>6944734</v>
+        <v>6944719</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,6 +2990,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>På stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea # På stående död sälg.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3010,7 +3030,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128802088</v>
+        <v>128802086</v>
       </c>
       <c r="B23" t="n">
         <v>80144</v>
@@ -3045,10 +3065,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558072</v>
+        <v>558041</v>
       </c>
       <c r="R23" t="n">
-        <v>6944719</v>
+        <v>6944734</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3091,26 +3111,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>På stående död sälg.</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Salix caprea # På stående död sälg.</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2079,7 +2079,7 @@
         <v>128802152</v>
       </c>
       <c r="B14" t="n">
-        <v>91080</v>
+        <v>91082</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>128802084</v>
       </c>
       <c r="B15" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>128802087</v>
       </c>
       <c r="B16" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>128802083</v>
       </c>
       <c r="B17" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>128802082</v>
       </c>
       <c r="B18" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>128802085</v>
       </c>
       <c r="B19" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>128802081</v>
       </c>
       <c r="B20" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>128802089</v>
       </c>
       <c r="B21" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128802088</v>
+        <v>128802086</v>
       </c>
       <c r="B22" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558072</v>
+        <v>558041</v>
       </c>
       <c r="R22" t="n">
-        <v>6944719</v>
+        <v>6944734</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,26 +2990,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>På stående död sälg.</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea # På stående död sälg.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3030,10 +3010,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128802086</v>
+        <v>128802088</v>
       </c>
       <c r="B23" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3065,10 +3045,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558041</v>
+        <v>558072</v>
       </c>
       <c r="R23" t="n">
-        <v>6944734</v>
+        <v>6944719</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,6 +3091,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>På stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea # På stående död sälg.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3134,7 +3134,7 @@
         <v>129092677</v>
       </c>
       <c r="B24" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>129092674</v>
       </c>
       <c r="B25" t="n">
-        <v>57675</v>
+        <v>57677</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>129092675</v>
       </c>
       <c r="B26" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2909,7 +2909,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128802086</v>
+        <v>128802088</v>
       </c>
       <c r="B22" t="n">
         <v>80146</v>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558041</v>
+        <v>558072</v>
       </c>
       <c r="R22" t="n">
-        <v>6944734</v>
+        <v>6944719</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,6 +2990,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>På stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Salix caprea # På stående död sälg.</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3010,7 +3030,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128802088</v>
+        <v>128802086</v>
       </c>
       <c r="B23" t="n">
         <v>80146</v>
@@ -3045,10 +3065,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558072</v>
+        <v>558041</v>
       </c>
       <c r="R23" t="n">
-        <v>6944719</v>
+        <v>6944734</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3091,26 +3111,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>På stående död sälg.</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Salix caprea # På stående död sälg.</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -2079,7 +2079,7 @@
         <v>128802152</v>
       </c>
       <c r="B14" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128802088</v>
+        <v>128802086</v>
       </c>
       <c r="B22" t="n">
         <v>80146</v>
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558072</v>
+        <v>558041</v>
       </c>
       <c r="R22" t="n">
-        <v>6944719</v>
+        <v>6944734</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,26 +2990,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>På stående död sälg.</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea # På stående död sälg.</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3030,7 +3010,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128802086</v>
+        <v>128802088</v>
       </c>
       <c r="B23" t="n">
         <v>80146</v>
@@ -3065,10 +3045,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558041</v>
+        <v>558072</v>
       </c>
       <c r="R23" t="n">
-        <v>6944734</v>
+        <v>6944719</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3111,6 +3091,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>På stående död sälg.</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Salix caprea # På stående död sälg.</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3232,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129092674</v>
+        <v>129092675</v>
       </c>
       <c r="B25" t="n">
-        <v>57677</v>
+        <v>80146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,21 +3243,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102110</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3267,13 +3267,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558159</v>
+        <v>558199</v>
       </c>
       <c r="R25" t="n">
-        <v>6944689</v>
+        <v>6944768</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129092675</v>
+        <v>129092674</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>57677</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>102110</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558199</v>
+        <v>558159</v>
       </c>
       <c r="R26" t="n">
-        <v>6944768</v>
+        <v>6944689</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -3232,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129092675</v>
+        <v>129092674</v>
       </c>
       <c r="B25" t="n">
-        <v>80146</v>
+        <v>57677</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,21 +3243,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>102110</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3267,13 +3267,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558199</v>
+        <v>558159</v>
       </c>
       <c r="R25" t="n">
-        <v>6944768</v>
+        <v>6944689</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129092674</v>
+        <v>129092675</v>
       </c>
       <c r="B26" t="n">
-        <v>57677</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102110</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558159</v>
+        <v>558199</v>
       </c>
       <c r="R26" t="n">
-        <v>6944689</v>
+        <v>6944768</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -3134,7 +3134,7 @@
         <v>129092677</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>129092675</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -3232,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129092674</v>
+        <v>129092675</v>
       </c>
       <c r="B25" t="n">
-        <v>57677</v>
+        <v>80148</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,21 +3243,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102110</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3267,13 +3267,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558159</v>
+        <v>558199</v>
       </c>
       <c r="R25" t="n">
-        <v>6944689</v>
+        <v>6944768</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129092675</v>
+        <v>129092674</v>
       </c>
       <c r="B26" t="n">
-        <v>80148</v>
+        <v>57677</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>102110</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558199</v>
+        <v>558159</v>
       </c>
       <c r="R26" t="n">
-        <v>6944768</v>
+        <v>6944689</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -3134,7 +3134,7 @@
         <v>129092677</v>
       </c>
       <c r="B24" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>129092675</v>
       </c>
       <c r="B25" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -3232,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129092675</v>
+        <v>129092674</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>57677</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,21 +3243,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>102110</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3267,13 +3267,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558199</v>
+        <v>558159</v>
       </c>
       <c r="R25" t="n">
-        <v>6944768</v>
+        <v>6944689</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129092674</v>
+        <v>129092675</v>
       </c>
       <c r="B26" t="n">
-        <v>57677</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102110</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558159</v>
+        <v>558199</v>
       </c>
       <c r="R26" t="n">
-        <v>6944689</v>
+        <v>6944768</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -3232,10 +3232,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129092674</v>
+        <v>129092675</v>
       </c>
       <c r="B25" t="n">
-        <v>57677</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,21 +3243,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102110</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3267,13 +3267,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558159</v>
+        <v>558199</v>
       </c>
       <c r="R25" t="n">
-        <v>6944689</v>
+        <v>6944768</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129092675</v>
+        <v>129092674</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>57677</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>102110</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558199</v>
+        <v>558159</v>
       </c>
       <c r="R26" t="n">
-        <v>6944768</v>
+        <v>6944689</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>124734950</v>
       </c>
       <c r="B12" t="n">
-        <v>57076</v>
+        <v>57078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>124734950</v>
       </c>
       <c r="B12" t="n">
-        <v>57078</v>
+        <v>57079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>124734950</v>
       </c>
       <c r="B12" t="n">
-        <v>57083</v>
+        <v>57089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>124734950</v>
       </c>
       <c r="B12" t="n">
-        <v>57089</v>
+        <v>57090</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -1818,7 +1818,7 @@
         <v>124734950</v>
       </c>
       <c r="B12" t="n">
-        <v>57090</v>
+        <v>57093</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33783-2025 artfynd.xlsx
+++ b/artfynd/A 33783-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128802152</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134635</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134639</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134640</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134641</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128802081</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128802082</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1469,6 +1509,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128802083</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128802084</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,6 +1741,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128802085</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1792,6 +1847,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128802086</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128802087</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2014,6 +2079,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128802088</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2115,6 +2185,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128802089</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2216,6 +2291,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092675</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2317,6 +2397,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092677</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2414,6 +2499,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134634</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134638</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2643,6 +2738,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108238544</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2771,6 +2871,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125381428</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2870,6 +2975,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129092674</t>
         </is>
       </c>
     </row>
@@ -2977,6 +3087,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84981824</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3105,6 +3220,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124734950</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3206,6 +3326,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134632</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3307,6 +3432,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134633</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3408,6 +3538,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134631</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3505,6 +3640,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134627</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3602,8 +3742,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81134646</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>